--- a/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_2005-2014_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2934854933333286</v>
+        <v>0.8190708387141336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>13555.71138768341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2934854933333286</v>
+        <v>0.8239058062100248</v>
       </c>
       <c r="G3" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2934854933333286</v>
+        <v>0.264957964774871</v>
       </c>
       <c r="I3" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2934854933333286</v>
+        <v>0.2106425636473267</v>
       </c>
       <c r="K3" t="n">
         <v>13555.71138768341</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>90.49451674079208</v>
+        <v>55.13711578891886</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>13555.71138768341</v>
       </c>
       <c r="F4" t="n">
-        <v>83.08780858066871</v>
+        <v>57.69477823035955</v>
       </c>
       <c r="G4" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="H4" t="n">
-        <v>64.51323295867209</v>
+        <v>55.31342630065346</v>
       </c>
       <c r="I4" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="J4" t="n">
-        <v>74.27028775746096</v>
+        <v>55.77634983767329</v>
       </c>
       <c r="K4" t="n">
         <v>13555.71138768341</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>95.26071009643709</v>
+        <v>61.93412837530271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>13555.71138768341</v>
       </c>
       <c r="F5" t="n">
-        <v>94.41866929607204</v>
+        <v>58.32962180133316</v>
       </c>
       <c r="G5" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="H5" t="n">
-        <v>64.51323295867209</v>
+        <v>61.68868276902323</v>
       </c>
       <c r="I5" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="J5" t="n">
-        <v>74.27028775746096</v>
+        <v>59.40919121586514</v>
       </c>
       <c r="K5" t="n">
         <v>13555.71138768341</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>95.26071009643711</v>
+        <v>77.49158574027173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>13555.71138768341</v>
       </c>
       <c r="F6" t="n">
-        <v>94.41866929607204</v>
+        <v>76.27811105824786</v>
       </c>
       <c r="G6" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="H6" t="n">
-        <v>64.51323295867209</v>
+        <v>77.40895528228198</v>
       </c>
       <c r="I6" t="n">
         <v>13555.71138768341</v>
       </c>
       <c r="J6" t="n">
-        <v>74.27028775746096</v>
+        <v>76.64155335614304</v>
       </c>
       <c r="K6" t="n">
         <v>13555.71138768341</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>10.84749976415593</v>
+        <v>15.81193678797052</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10.84749976415593</v>
+        <v>15.81193678797052</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>14.26481742531124</v>
+        <v>20.79321468770852</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>14.26481742531124</v>
+        <v>20.79321468770852</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>15.84959725015053</v>
+        <v>23.10328050545685</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>15.84959725015053</v>
+        <v>23.10328050545685</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>16.74375782662586</v>
+        <v>24.40666016168342</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>16.74375782662586</v>
+        <v>24.40666016168342</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>20.33356708152512</v>
+        <v>29.63937168539326</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>17.31354852946134</v>
+        <v>25.23721971655691</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>17.31354852946134</v>
+        <v>25.23721971655691</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002593569557647059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002593569557647059</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002593569557647059</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002593569557647059</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002793074908235294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002793074908235294</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002793074908235294</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004189612362352942</v>
+        <v>0.002793074908235294</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005386644465882354</v>
+        <v>0.004389117712941176</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.01375713249999978</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>3.561170508</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.01375713249999978</v>
       </c>
       <c r="G18" t="n">
         <v>3.561170508</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.06849440336011614</v>
       </c>
       <c r="I18" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.07900045254371098</v>
       </c>
       <c r="K18" t="n">
         <v>3.561170508</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.9172087773904717</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>3.561170508</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.9377743972539639</v>
       </c>
       <c r="G19" t="n">
         <v>3.561170508</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.6398243609206286</v>
       </c>
       <c r="I19" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.6315580328000262</v>
       </c>
       <c r="K19" t="n">
         <v>3.561170508</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.9172087773904717</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>3.561170508</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.9377743972539639</v>
       </c>
       <c r="G20" t="n">
         <v>3.561170508</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.6398243609206286</v>
       </c>
       <c r="I20" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.6315580328000262</v>
       </c>
       <c r="K20" t="n">
         <v>3.561170508</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.9034516448904719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>3.561170508</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.9240172647539642</v>
       </c>
       <c r="G21" t="n">
         <v>3.561170508</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.5713299575605124</v>
       </c>
       <c r="I21" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.5525575802563152</v>
       </c>
       <c r="K21" t="n">
         <v>3.561170508</v>
@@ -1513,13 +1513,13 @@
         <v>3.561170508</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.185874498301402</v>
       </c>
       <c r="I29" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2036915842625959</v>
       </c>
       <c r="K29" t="n">
         <v>3.561170508</v>
@@ -1550,13 +1550,13 @@
         <v>3.561170508</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.185874498301402</v>
       </c>
       <c r="I30" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.2036915842625959</v>
       </c>
       <c r="K30" t="n">
         <v>3.561170508</v>
@@ -1587,13 +1587,13 @@
         <v>3.561170508</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.1858744983014021</v>
       </c>
       <c r="I31" t="n">
         <v>3.561170508</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2036915842625959</v>
       </c>
       <c r="K31" t="n">
         <v>3.561170508</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>5.628152463511629</v>
+        <v>5.508134656932496</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F54" t="n">
-        <v>5.502458332869973</v>
+        <v>5.349017039437125</v>
       </c>
       <c r="G54" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H54" t="n">
-        <v>5.467361348165712</v>
+        <v>5.512960579834766</v>
       </c>
       <c r="I54" t="n">
         <v>9.14682316066958</v>
       </c>
       <c r="J54" t="n">
-        <v>5.569523085349913</v>
+        <v>5.37518363817932</v>
       </c>
       <c r="K54" t="n">
         <v>9.14682316066958</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>6.523015873015873</v>
+        <v>6.444280939661925</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F55" t="n">
-        <v>6.252512875912547</v>
+        <v>6.34305307786183</v>
       </c>
       <c r="G55" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H55" t="n">
-        <v>5.843505174776133</v>
+        <v>6.437562669940217</v>
       </c>
       <c r="I55" t="n">
         <v>9.955665995997498</v>
       </c>
       <c r="J55" t="n">
-        <v>6.469770410055795</v>
+        <v>6.333612046114108</v>
       </c>
       <c r="K55" t="n">
         <v>9.955665995997498</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>6.545205249030221</v>
+        <v>6.444280939661924</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F56" t="n">
-        <v>6.252512875912547</v>
+        <v>6.343053077861829</v>
       </c>
       <c r="G56" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H56" t="n">
-        <v>5.843505174776133</v>
+        <v>6.437562669940218</v>
       </c>
       <c r="I56" t="n">
         <v>10.4988316414091</v>
       </c>
       <c r="J56" t="n">
-        <v>6.469770410055795</v>
+        <v>6.333612046114108</v>
       </c>
       <c r="K56" t="n">
         <v>10.4988316414091</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>3.69869868431638</v>
+        <v>1.800681389238592</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F64" t="n">
-        <v>3.987776083196049</v>
+        <v>1.93577135453622</v>
       </c>
       <c r="G64" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H64" t="n">
-        <v>4.43260635367965</v>
+        <v>1.794199138438582</v>
       </c>
       <c r="I64" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="J64" t="n">
-        <v>4.115215466522164</v>
+        <v>1.927627200601003</v>
       </c>
       <c r="K64" t="n">
         <v>18.78580346421998</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>3.69869868431638</v>
+        <v>1.800681389238592</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F65" t="n">
-        <v>3.987776083196049</v>
+        <v>1.93577135453622</v>
       </c>
       <c r="G65" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H65" t="n">
-        <v>5.056462527069229</v>
+        <v>1.809705468188911</v>
       </c>
       <c r="I65" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="J65" t="n">
-        <v>4.214968141816283</v>
+        <v>1.935070501258221</v>
       </c>
       <c r="K65" t="n">
         <v>18.78580346421998</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.200774594674813</v>
+        <v>1.800681389238592</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>18.78580346421998</v>
       </c>
       <c r="F66" t="n">
-        <v>4.512041397212304</v>
+        <v>1.93577135453622</v>
       </c>
       <c r="G66" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="H66" t="n">
-        <v>5.580727841085482</v>
+        <v>1.809705468188911</v>
       </c>
       <c r="I66" t="n">
         <v>18.78580346421998</v>
       </c>
       <c r="J66" t="n">
-        <v>4.739233455832537</v>
+        <v>1.935070501258221</v>
       </c>
       <c r="K66" t="n">
         <v>18.78580346421998</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4106756611487163</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4106756611487163</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.715723684160384</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.715723684160384</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9682471125407942</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9682471125407942</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1.184367122315215</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.184367122315215</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1.372598487585017</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.372598487585017</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4106756611487163</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4106756611487163</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.715723684160384</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.715723684160384</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9682471125407942</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9682471125407942</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1.184367122315215</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.184367122315215</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1.372598487585017</v>
+        <v>18.78580346421998</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.372598487585017</v>
+        <v>18.78580346421998</v>
       </c>
     </row>
     <row r="82">
